--- a/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Syracuse_20251107.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Syracuse_20251107.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>281.92</t>
+          <t>140.96</t>
         </is>
       </c>
     </row>
